--- a/ZonasEscolares/excels/LA_LIBERTAD-OTUZCO-OTUZCO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-OTUZCO-OTUZCO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LA_LIBERTAD-OTUZCO-OTUZCO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-OTUZCO-OTUZCO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>80229 CRISTO JESUS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-7.90339</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.56631</v>
-      </c>
-      <c r="I2" t="n">
-        <v>507</v>
-      </c>
-      <c r="J2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-7.90339</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.56631</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>80288</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-7.909951</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.49901</v>
-      </c>
-      <c r="I3" t="n">
-        <v>342</v>
-      </c>
-      <c r="J3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-7.909951</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.49901</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>80289</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-7.867989</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.509885</v>
-      </c>
-      <c r="I4" t="n">
-        <v>202</v>
-      </c>
-      <c r="J4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-7.867989</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.509885</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>80662</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-7.771344</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.59381</v>
-      </c>
-      <c r="I5" t="n">
-        <v>289</v>
-      </c>
-      <c r="J5" t="n">
-        <v>23</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-7.771344</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.59381</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>81028 JUAN ALVARADO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-7.9022</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.5663</v>
-      </c>
-      <c r="I6" t="n">
-        <v>852</v>
-      </c>
-      <c r="J6" t="n">
-        <v>51</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-7.9022</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.5663</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>INMACULADA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-7.90874</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.56619999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>443</v>
-      </c>
-      <c r="J7" t="n">
-        <v>14</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-7.90874</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.5662</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-7.907946</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.563545</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1056</v>
-      </c>
-      <c r="J8" t="n">
-        <v>67</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-7.907946</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.563545</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1056</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>81550</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-7.933858</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-78.479857</v>
-      </c>
-      <c r="I9" t="n">
-        <v>318</v>
-      </c>
-      <c r="J9" t="n">
-        <v>31</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-7.933858</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-78.479857</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>81915</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-8.004327</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.60485199999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-8.004327</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.604852</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>80910</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-7.885944</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-78.37965699999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>271</v>
-      </c>
-      <c r="J11" t="n">
-        <v>18</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-7.885944</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-78.379657</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LA_LIBERTAD-OTUZCO-OTUZCO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-OTUZCO-OTUZCO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>261238</t>
+          <t>261691</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>80229 CRISTO JESUS</t>
+          <t>INMACULADA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-7.90339</t>
+          <t>-7.90874</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.56631</t>
+          <t>-78.5662</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>443</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>261399</t>
+          <t>261403</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>80288</t>
+          <t>80289</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.909951</t>
+          <t>-7.867989</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.49901</t>
+          <t>-78.509885</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>261403</t>
+          <t>264010</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>80289</t>
+          <t>80910</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-7.867989</t>
+          <t>-7.885944</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.509885</t>
+          <t>-78.379657</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>261568</t>
+          <t>261238</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80662</t>
+          <t>80229 CRISTO JESUS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.771344</t>
+          <t>-7.90339</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.59381</t>
+          <t>-78.56631</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>507</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>261686</t>
+          <t>261568</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>81028 JUAN ALVARADO</t>
+          <t>80662</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-7.9022</t>
+          <t>-7.771344</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.5663</t>
+          <t>-78.59381</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>289</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>261691</t>
+          <t>263223</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>INMACULADA VIRGEN DE LA PUERTA</t>
+          <t>81915</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.90874</t>
+          <t>-8.004327</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.5662</t>
+          <t>-78.604852</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>261709</t>
+          <t>261399</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SIMON BOLIVAR</t>
+          <t>80288</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.907946</t>
+          <t>-7.909951</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.563545</t>
+          <t>-78.49901</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>342</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>263223</t>
+          <t>261686</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>81915</t>
+          <t>81028 JUAN ALVARADO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.004327</t>
+          <t>-7.9022</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.604852</t>
+          <t>-78.5663</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>852</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>264010</t>
+          <t>261709</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>80910</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-7.885944</t>
+          <t>-7.907946</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.379657</t>
+          <t>-78.563545</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-OTUZCO-OTUZCO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-OTUZCO-OTUZCO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>261691</t>
+          <t>264010</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>INMACULADA VIRGEN DE LA PUERTA</t>
+          <t>80910</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-7.90874</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.5662</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>-7.885944</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.379657</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>261403</t>
+          <t>263223</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>80289</t>
+          <t>81915</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.867989</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.509885</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-8.004327</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-78.604852</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>264010</t>
+          <t>262092</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>80910</t>
+          <t>81550</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-7.885944</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.379657</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-7.933858</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.479857</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>261238</t>
+          <t>261709</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80229 CRISTO JESUS</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.90339</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.56631</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>-7.907946</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-78.563545</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>261568</t>
+          <t>261691</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>80662</t>
+          <t>INMACULADA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-7.771344</t>
+          <t>443</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.59381</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>-7.90874</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-78.5662</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>263223</t>
+          <t>261686</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>81915</t>
+          <t>81028 JUAN ALVARADO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.004327</t>
+          <t>852</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.604852</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-7.9022</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-78.5663</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>261399</t>
+          <t>261568</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80288</t>
+          <t>80662</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.909951</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.49901</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-7.771344</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-78.59381</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>262092</t>
+          <t>261403</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>81550</t>
+          <t>80289</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7.933858</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.479857</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>-7.867989</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.509885</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>261686</t>
+          <t>261399</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>81028 JUAN ALVARADO</t>
+          <t>80288</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-7.9022</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.5663</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>-7.909951</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-78.49901</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>261709</t>
+          <t>261238</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SIMON BOLIVAR</t>
+          <t>80229 CRISTO JESUS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-7.907946</t>
+          <t>507</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.563545</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>-7.90339</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-78.56631</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-OTUZCO-OTUZCO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-OTUZCO-OTUZCO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
